--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.09120691808462</v>
+        <v>7.48982112418875</v>
       </c>
       <c r="D2" t="n">
-        <v>12.63819751784999</v>
+        <v>2.053707096650624</v>
       </c>
       <c r="E2" t="n">
-        <v>11.12870271028555</v>
+        <v>1.808414190421402</v>
       </c>
       <c r="F2" t="n">
-        <v>21.50653068796871</v>
+        <v>3.494811236794915</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.38869006632535</v>
+        <v>5.42566213577787</v>
       </c>
       <c r="D3" t="n">
-        <v>32.41486898537143</v>
+        <v>5.267416210122859</v>
       </c>
       <c r="E3" t="n">
-        <v>11.12870271028555</v>
+        <v>1.808414190421402</v>
       </c>
       <c r="F3" t="n">
-        <v>21.50653068796871</v>
+        <v>3.494811236794915</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.0938684369077</v>
+        <v>6.515253620997501</v>
       </c>
       <c r="D4" t="n">
-        <v>38.6730934309257</v>
+        <v>6.284377682525427</v>
       </c>
       <c r="E4" t="n">
-        <v>11.12870271028555</v>
+        <v>1.808414190421402</v>
       </c>
       <c r="F4" t="n">
-        <v>21.50653068796871</v>
+        <v>3.494811236794915</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.37052299906568</v>
+        <v>5.422709987348173</v>
       </c>
       <c r="D5" t="n">
-        <v>16.27882059609971</v>
+        <v>2.645308346866202</v>
       </c>
       <c r="E5" t="n">
-        <v>11.12870271028555</v>
+        <v>1.808414190421402</v>
       </c>
       <c r="F5" t="n">
-        <v>21.50653068796871</v>
+        <v>3.494811236794915</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.88227584446782</v>
+        <v>3.393369824726022</v>
       </c>
       <c r="D6" t="n">
-        <v>57.2374440379722</v>
+        <v>9.301084656170483</v>
       </c>
       <c r="E6" t="n">
-        <v>11.12870271028555</v>
+        <v>1.808414190421402</v>
       </c>
       <c r="F6" t="n">
-        <v>21.50653068796871</v>
+        <v>3.494811236794915</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.71071457939895</v>
+        <v>2.877991119152329</v>
       </c>
       <c r="D7" t="n">
-        <v>17.07288280258686</v>
+        <v>2.774343455420365</v>
       </c>
       <c r="E7" t="n">
-        <v>11.12870271028555</v>
+        <v>1.808414190421402</v>
       </c>
       <c r="F7" t="n">
-        <v>21.50653068796871</v>
+        <v>3.494811236794915</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.71481545909484</v>
+        <v>2.391157512102911</v>
       </c>
       <c r="D8" t="n">
-        <v>13.54974017752292</v>
+        <v>2.201832778847474</v>
       </c>
       <c r="E8" t="n">
-        <v>11.12870271028555</v>
+        <v>1.808414190421402</v>
       </c>
       <c r="F8" t="n">
-        <v>21.50653068796871</v>
+        <v>3.494811236794915</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.75518161975904</v>
+        <v>2.722717013210844</v>
       </c>
       <c r="D9" t="n">
-        <v>74.88407707917618</v>
+        <v>12.16866252536613</v>
       </c>
       <c r="E9" t="n">
-        <v>11.12870271028555</v>
+        <v>1.808414190421402</v>
       </c>
       <c r="F9" t="n">
-        <v>21.50653068796871</v>
+        <v>3.494811236794915</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
